--- a/Localizaciones_Final.xlsx
+++ b/Localizaciones_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\OneDrive\Escritorio\Dashboard_Descargas_Atmosfericas_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD407E1D-54E3-4E1A-91C6-82355DE27B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC29001-4088-4C1A-84E8-F28F69516768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F0EA1A3-7710-45F5-AD22-CF7441E52F7C}"/>
   </bookViews>
